--- a/docs/ua/modules/arch/attachments/architecture/platform-system-requirements/registry-cost-calculator.xlsx
+++ b/docs/ua/modules/arch/attachments/architecture/platform-system-requirements/registry-cost-calculator.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10514"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10512"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Maksym_Kharchenko/Work/Development/mdtu-ddm/mdtu-ddm-gerrit-workspace/mdtu-ddm/general/ddm-architecture/docs/ua/modules/arch/attachments/architecture/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Maksym_Kharchenko/Work/Development/mdtu-ddm/mdtu-ddm-gerrit-workspace/mdtu-ddm/general/ddm-architecture/docs/ua/modules/arch/attachments/architecture/platform-system-requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF37101B-D7D8-8F4B-AB73-DAB13B4B6AD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F0CB933-87EA-8C44-847B-0CE880E6DE69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" activeTab="2" xr2:uid="{27F18D04-7E62-4946-83A8-E11013D50C84}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{27F18D04-7E62-4946-83A8-E11013D50C84}"/>
   </bookViews>
   <sheets>
     <sheet name="Калькулятор вартості" sheetId="1" r:id="rId1"/>
@@ -641,9 +641,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -681,7 +681,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -787,7 +787,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -929,7 +929,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1165,11 +1165,11 @@
       </c>
       <c r="U8" s="28">
         <f>J$24/$B$4*C8</f>
-        <v>129.26185000000001</v>
+        <v>116.83035</v>
       </c>
       <c r="V8" s="15">
         <f>T8+U8</f>
-        <v>319.62585000000001</v>
+        <v>307.19434999999999</v>
       </c>
     </row>
     <row r="9" spans="1:22" ht="18" x14ac:dyDescent="0.25">
@@ -1244,11 +1244,11 @@
       </c>
       <c r="U9" s="28">
         <f>J$24/$B$4*C9</f>
-        <v>258.52370000000002</v>
+        <v>233.66069999999999</v>
       </c>
       <c r="V9" s="15">
         <f>T9+U9</f>
-        <v>570.71170000000006</v>
+        <v>545.84870000000001</v>
       </c>
     </row>
     <row r="10" spans="1:22" ht="18" x14ac:dyDescent="0.25">
@@ -1323,11 +1323,11 @@
       </c>
       <c r="U10" s="28">
         <f>J$24/$B$4*C10</f>
-        <v>646.30925000000002</v>
+        <v>584.15174999999999</v>
       </c>
       <c r="V10" s="15">
         <f t="shared" ref="V10:V11" si="0">T10+U10</f>
-        <v>1323.9692500000001</v>
+        <v>1261.8117500000001</v>
       </c>
     </row>
     <row r="11" spans="1:22" ht="18" x14ac:dyDescent="0.25">
@@ -1402,11 +1402,11 @@
       </c>
       <c r="U11" s="28">
         <f t="shared" ref="U11" si="2">J$24/$B$4*C11</f>
-        <v>1292.6185</v>
+        <v>1168.3035</v>
       </c>
       <c r="V11" s="15">
         <f t="shared" si="0"/>
-        <v>2579.3985000000002</v>
+        <v>2455.0835000000002</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.2">
@@ -1570,14 +1570,14 @@
         <v>38</v>
       </c>
       <c r="C20" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D20" s="3">
         <v>0.60799999999999998</v>
       </c>
       <c r="E20" s="3">
         <f t="shared" si="3"/>
-        <v>3.04</v>
+        <v>1.8239999999999998</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>39</v>
@@ -1591,11 +1591,11 @@
       </c>
       <c r="I20" s="27">
         <f t="shared" si="4"/>
-        <v>148.75</v>
+        <v>89.25</v>
       </c>
       <c r="J20" s="3">
         <f t="shared" si="5"/>
-        <v>2337.5500000000002</v>
+        <v>1402.53</v>
       </c>
     </row>
     <row r="21" spans="1:10" s="21" customFormat="1" x14ac:dyDescent="0.2">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="J24" s="15">
         <f>SUM(J17:J23)+SUM(I17:I23)</f>
-        <v>10340.948</v>
+        <v>9346.4279999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="C2">
         <f>B2*C6*720*'Калькулятор вартості'!E8+B2*'Калькулятор вартості'!I8+'Калькулятор вартості'!M8+'Калькулятор вартості'!S8+B2*'Калькулятор вартості'!U8</f>
-        <v>570.71170000000006</v>
+        <v>545.84870000000001</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -2855,12 +2855,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="346a80a9-3278-4844-b436-58ae57568790">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="a2d094e0-efa8-4820-a0b3-29af30f3c512" xsi:nil="true"/>
+    <SharedWithUsers xmlns="a2d094e0-efa8-4820-a0b3-29af30f3c512">
+      <UserInfo>
+        <DisplayName>Vitalii Fedorenko</DisplayName>
+        <AccountId>158</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Oleksandr Zakusylo</DisplayName>
+        <AccountId>159</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <Capability_x0020_name xmlns="346a80a9-3278-4844-b436-58ae57568790"/>
+    <Release xmlns="346a80a9-3278-4844-b436-58ae57568790" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3123,34 +3139,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="346a80a9-3278-4844-b436-58ae57568790">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="a2d094e0-efa8-4820-a0b3-29af30f3c512" xsi:nil="true"/>
-    <SharedWithUsers xmlns="a2d094e0-efa8-4820-a0b3-29af30f3c512">
-      <UserInfo>
-        <DisplayName>Vitalii Fedorenko</DisplayName>
-        <AccountId>158</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Oleksandr Zakusylo</DisplayName>
-        <AccountId>159</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <Capability_x0020_name xmlns="346a80a9-3278-4844-b436-58ae57568790"/>
-    <Release xmlns="346a80a9-3278-4844-b436-58ae57568790" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92FEC7CF-4815-42BA-A053-9D2F9AB7FD60}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD363066-8CBD-4D6F-8835-7EB8A1E12EC9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="346a80a9-3278-4844-b436-58ae57568790"/>
+    <ds:schemaRef ds:uri="a2d094e0-efa8-4820-a0b3-29af30f3c512"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3175,12 +3178,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD363066-8CBD-4D6F-8835-7EB8A1E12EC9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92FEC7CF-4815-42BA-A053-9D2F9AB7FD60}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="346a80a9-3278-4844-b436-58ae57568790"/>
-    <ds:schemaRef ds:uri="a2d094e0-efa8-4820-a0b3-29af30f3c512"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>